--- a/testakten/markenrechte-sicherungsuebertragung-insolvenz-mannheim/20_IP_Inventar_Insolvenzverwaltung.xlsx
+++ b/testakten/markenrechte-sicherungsuebertragung-insolvenz-mannheim/20_IP_Inventar_Insolvenzverwaltung.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registrierte_Rechte" sheetId="1" r:id="Rad2fd249fe3444d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weitere_Assets" sheetId="2" r:id="Ra67ab4e152584ae1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offene_Unterlagen" sheetId="3" r:id="Ree85b06930fe4707"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registrierte_Rechte" sheetId="1" r:id="Rf44c36e3a0474097"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weitere_Assets" sheetId="2" r:id="R4594fcb043634454"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offene_Unterlagen" sheetId="3" r:id="Rc27ec4810ab84eeb"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/testakten/markenrechte-sicherungsuebertragung-insolvenz-mannheim/20_IP_Inventar_Insolvenzverwaltung.xlsx
+++ b/testakten/markenrechte-sicherungsuebertragung-insolvenz-mannheim/20_IP_Inventar_Insolvenzverwaltung.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registrierte_Rechte" sheetId="1" r:id="Rf44c36e3a0474097"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weitere_Assets" sheetId="2" r:id="R4594fcb043634454"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offene_Unterlagen" sheetId="3" r:id="Rc27ec4810ab84eeb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registrierte_Rechte" sheetId="1" r:id="R0d88b9df980e4db4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weitere_Assets" sheetId="2" r:id="R4c8423ea0d644e4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offene_Unterlagen" sheetId="3" r:id="Rd588b87c1a0941d9"/>
   </x:sheets>
 </x:workbook>
 </file>
